--- a/input_home.xlsx
+++ b/input_home.xlsx
@@ -421,43 +421,43 @@
         <v>24</v>
       </c>
       <c r="B1" t="n">
-        <v>60.20929263530426</v>
+        <v>14.86486721351971</v>
       </c>
       <c r="C1" t="n">
-        <v>0.005833536372007393</v>
+        <v>0.9336343207222382</v>
       </c>
       <c r="D1" t="n">
-        <v>0.1796667004974809</v>
+        <v>0.002863745783304669</v>
       </c>
       <c r="E1" t="n">
-        <v>5.814523890988209</v>
+        <v>3.247202298058066</v>
       </c>
       <c r="F1" t="n">
-        <v>0.6181473331762545</v>
+        <v>0.6769653741861182</v>
       </c>
       <c r="G1" t="n">
-        <v>2.953850063815602</v>
+        <v>42.27630672670247</v>
       </c>
       <c r="H1" t="n">
-        <v>4.1969282432547</v>
+        <v>3.588779763383489</v>
       </c>
       <c r="I1" t="n">
-        <v>3.148080693066397</v>
+        <v>4.886391066817031</v>
       </c>
       <c r="J1" t="n">
-        <v>5.793723095253834</v>
+        <v>5.516825164077503</v>
       </c>
       <c r="K1" t="n">
-        <v>3.102329553028823</v>
+        <v>2.113346937070531</v>
       </c>
       <c r="L1" t="n">
-        <v>1.992428264736988</v>
+        <v>5.030597429359485</v>
       </c>
       <c r="M1" t="n">
-        <v>3.729914446166711</v>
+        <v>1.467500571600376</v>
       </c>
       <c r="N1" t="n">
-        <v>5.22622848034116</v>
+        <v>5.86709002576029</v>
       </c>
       <c r="O1" t="n">
         <v>104.65</v>
@@ -472,7 +472,7 @@
         <v>0.35</v>
       </c>
       <c r="S1" t="n">
-        <v>3.017552506580594</v>
+        <v>1.524914114449834</v>
       </c>
       <c r="T1" t="n">
         <v>0</v>
@@ -481,22 +481,22 @@
         <v>0</v>
       </c>
       <c r="V1" t="n">
-        <v>32.78330020426333</v>
+        <v>2.733646402136745</v>
       </c>
       <c r="W1" t="n">
         <v>100000</v>
       </c>
       <c r="X1" t="n">
-        <v>78.36468041789972</v>
+        <v>4.960232915996539</v>
       </c>
       <c r="Y1" t="n">
-        <v>0.02273134118030032</v>
+        <v>0.2985046546352792</v>
       </c>
       <c r="Z1" t="n">
-        <v>0.02489253423493876</v>
+        <v>0.1432043512639642</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.08622661103760791</v>
+        <v>0.2700890467620114</v>
       </c>
       <c r="AB1" t="n">
         <v>0.7</v>
@@ -505,16 +505,16 @@
         <v>0.5</v>
       </c>
       <c r="AD1" t="n">
-        <v>0.02622640682716464</v>
+        <v>0.143393898043621</v>
       </c>
       <c r="AE1" t="n">
-        <v>48.5925597250899</v>
+        <v>47.22672727923468</v>
       </c>
       <c r="AF1" t="n">
-        <v>43.59466249977771</v>
+        <v>70.37851393134741</v>
       </c>
       <c r="AG1" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="AH1" t="n">
         <v>0.11</v>
@@ -523,22 +523,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ1" t="n">
-        <v>1.025714775293226</v>
+        <v>3.245646382518976</v>
       </c>
       <c r="AK1" t="n">
-        <v>3.569062220073512</v>
+        <v>7.277586598248925</v>
       </c>
       <c r="AL1" t="n">
         <v>0</v>
       </c>
       <c r="AM1" t="n">
-        <v>3.604515277309995</v>
+        <v>2.137486532436598</v>
       </c>
       <c r="AN1" t="n">
-        <v>35.43341792516593</v>
+        <v>23.16998157788103</v>
       </c>
       <c r="AO1" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP1" t="n">
         <v>0.11</v>
@@ -547,22 +547,22 @@
         <v>1.3</v>
       </c>
       <c r="AR1" t="n">
-        <v>45.06496369887362</v>
+        <v>20.12661839428246</v>
       </c>
       <c r="AS1" t="n">
-        <v>26.11301835328726</v>
+        <v>1.03334506693412</v>
       </c>
       <c r="AT1" t="n">
-        <v>1.400462849023332</v>
+        <v>22.07492619901768</v>
       </c>
       <c r="AU1" t="n">
-        <v>3.09245122489967</v>
+        <v>23.47586100270521</v>
       </c>
       <c r="AV1" t="n">
-        <v>4.718975355047474</v>
+        <v>16.9303283669795</v>
       </c>
       <c r="AW1" t="n">
-        <v>2.947545504007369</v>
+        <v>1.992384137057159</v>
       </c>
       <c r="AX1" t="n">
         <v>125</v>
@@ -624,43 +624,43 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>4.66611195423704</v>
+        <v>73.2664522309028</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01299900133279407</v>
+        <v>0.007406548483288461</v>
       </c>
       <c r="D2" t="n">
-        <v>0.192637135495374</v>
+        <v>0.3588793699996433</v>
       </c>
       <c r="E2" t="n">
-        <v>6.73826945069528</v>
+        <v>9.396797552664831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002944587498445029</v>
+        <v>0.1019285297386612</v>
       </c>
       <c r="G2" t="n">
-        <v>23.8710365083291</v>
+        <v>1.50891518167804</v>
       </c>
       <c r="H2" t="n">
-        <v>3.171876494815056</v>
+        <v>1.993820345254216</v>
       </c>
       <c r="I2" t="n">
-        <v>4.867990368023559</v>
+        <v>2.729923506468542</v>
       </c>
       <c r="J2" t="n">
-        <v>8.821335317475178</v>
+        <v>5.285696788353456</v>
       </c>
       <c r="K2" t="n">
-        <v>2.855254182596006</v>
+        <v>1.346899386375183</v>
       </c>
       <c r="L2" t="n">
-        <v>1.725100211201428</v>
+        <v>1.364877334373306</v>
       </c>
       <c r="M2" t="n">
-        <v>1.132880085730618</v>
+        <v>1.321321698950693</v>
       </c>
       <c r="N2" t="n">
-        <v>1.308302512632248</v>
+        <v>2.599675386657246</v>
       </c>
       <c r="O2" t="n">
         <v>104.65</v>
@@ -675,7 +675,7 @@
         <v>0.35</v>
       </c>
       <c r="S2" t="n">
-        <v>4.834724640718763</v>
+        <v>1.101075956870546</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -684,22 +684,22 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>37.42953284612236</v>
+        <v>3.543535970209363</v>
       </c>
       <c r="W2" t="n">
         <v>100000</v>
       </c>
       <c r="X2" t="n">
-        <v>38.83373164221212</v>
+        <v>21.2209154372387</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3561682361449876</v>
+        <v>0.7280906459209183</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002968914138766124</v>
+        <v>0.2531630668203078</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004082836889764518</v>
+        <v>0.1029312486126932</v>
       </c>
       <c r="AB2" t="n">
         <v>0.7</v>
@@ -708,13 +708,13 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.001591443692785996</v>
+        <v>0.008073156798270359</v>
       </c>
       <c r="AE2" t="n">
-        <v>47.23322315667259</v>
+        <v>47.56138026838401</v>
       </c>
       <c r="AF2" t="n">
-        <v>85.48742196566388</v>
+        <v>56.42299867973075</v>
       </c>
       <c r="AG2" t="n">
         <v>0.5</v>
@@ -726,22 +726,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.592231178808961</v>
+        <v>1.029925089146845</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.535758348307656</v>
+        <v>8.765634717174986</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.843336614606088</v>
+        <v>2.19461678567519</v>
       </c>
       <c r="AN2" t="n">
-        <v>13.16061368534579</v>
+        <v>37.32619859399745</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AP2" t="n">
         <v>0.11</v>
@@ -750,22 +750,22 @@
         <v>1.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.961318601467333</v>
+        <v>46.62483392029357</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.22441754360365</v>
+        <v>0.650513568311224</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.25805159821976</v>
+        <v>30.97739601118172</v>
       </c>
       <c r="AU2" t="n">
-        <v>69.3758136683593</v>
+        <v>6.046920847580861</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.75320336378103</v>
+        <v>10.83602894660395</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.54219691262129</v>
+        <v>27.00831548307504</v>
       </c>
       <c r="AX2" t="n">
         <v>125</v>
@@ -827,43 +827,43 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>95.92793853189167</v>
+        <v>49.42509733655319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03991509145388229</v>
+        <v>0.0282135832799881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08623616506275689</v>
+        <v>0.08507449727332718</v>
       </c>
       <c r="E3" t="n">
-        <v>1.163268893181148</v>
+        <v>27.48599978954534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5134345014701349</v>
+        <v>0.1523907121541738</v>
       </c>
       <c r="G3" t="n">
-        <v>3.299094866983565</v>
+        <v>2.997981245713293</v>
       </c>
       <c r="H3" t="n">
-        <v>1.664618249984747</v>
+        <v>6.243373155575673</v>
       </c>
       <c r="I3" t="n">
-        <v>2.166601462348472</v>
+        <v>1.362608683023906</v>
       </c>
       <c r="J3" t="n">
-        <v>5.961946002315083</v>
+        <v>1.843653870670102</v>
       </c>
       <c r="K3" t="n">
-        <v>8.229138750940967</v>
+        <v>2.026825982952242</v>
       </c>
       <c r="L3" t="n">
-        <v>7.805836459946332</v>
+        <v>2.892700212732175</v>
       </c>
       <c r="M3" t="n">
-        <v>2.610658862812501</v>
+        <v>1.405605159610745</v>
       </c>
       <c r="N3" t="n">
-        <v>2.885899945957752</v>
+        <v>4.65841304990888</v>
       </c>
       <c r="O3" t="n">
         <v>104.65</v>
@@ -878,7 +878,7 @@
         <v>0.35</v>
       </c>
       <c r="S3" t="n">
-        <v>1.135572463054289</v>
+        <v>8.93503761077327</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -887,22 +887,22 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4.537532224365643</v>
+        <v>3.076436989131095</v>
       </c>
       <c r="W3" t="n">
         <v>100000</v>
       </c>
       <c r="X3" t="n">
-        <v>3.702141437211307</v>
+        <v>56.19598876813254</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.174935556699278</v>
+        <v>0.5290166013632849</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001279766540559395</v>
+        <v>0.3696105182137062</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2603755278681098</v>
+        <v>0.004457041920171548</v>
       </c>
       <c r="AB3" t="n">
         <v>0.7</v>
@@ -911,16 +911,16 @@
         <v>0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05484266280060737</v>
+        <v>0.1898142125211391</v>
       </c>
       <c r="AE3" t="n">
-        <v>47.89864257626776</v>
+        <v>47.06412312783145</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.85003911002539</v>
+        <v>27.27968652117235</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="AH3" t="n">
         <v>0.11</v>
@@ -929,22 +929,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.775522320608392</v>
+        <v>1.623598935333417</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.145857499167094</v>
+        <v>8.961207346070555</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.45190164495274</v>
+        <v>1.14835980629361</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.07573888412047</v>
+        <v>23.72641395850215</v>
       </c>
       <c r="AO3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
         <v>0.11</v>
@@ -953,22 +953,22 @@
         <v>1.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.986410970750008</v>
+        <v>16.31200199025767</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.726205161922211</v>
+        <v>0.8219090261868272</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.955157938481161</v>
+        <v>5.695404845873487</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.343500349012304</v>
+        <v>24.89852358332788</v>
       </c>
       <c r="AV3" t="n">
-        <v>135.2436753138714</v>
+        <v>168.9232666736632</v>
       </c>
       <c r="AW3" t="n">
-        <v>79.75833299828544</v>
+        <v>3.337114357632195</v>
       </c>
       <c r="AX3" t="n">
         <v>125</v>
@@ -1030,43 +1030,43 @@
         <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>1.181845876233888</v>
+        <v>16.51520890538957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2706922610721967</v>
+        <v>0.05752826012772017</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3409879041698753</v>
+        <v>0.146143092658319</v>
       </c>
       <c r="E4" t="n">
-        <v>1.087533886390222</v>
+        <v>24.87778906487593</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03206797884990244</v>
+        <v>0.9081841602017848</v>
       </c>
       <c r="G4" t="n">
-        <v>1.284440685026492</v>
+        <v>9.394484915689429</v>
       </c>
       <c r="H4" t="n">
-        <v>4.469454186786914</v>
+        <v>5.273342009853708</v>
       </c>
       <c r="I4" t="n">
-        <v>1.620074357399148</v>
+        <v>5.104052138219193</v>
       </c>
       <c r="J4" t="n">
-        <v>4.957989933159753</v>
+        <v>1.218727222321652</v>
       </c>
       <c r="K4" t="n">
-        <v>4.637610387176005</v>
+        <v>6.966668014552873</v>
       </c>
       <c r="L4" t="n">
-        <v>2.45091972918393</v>
+        <v>2.778170507924004</v>
       </c>
       <c r="M4" t="n">
-        <v>1.886511957059772</v>
+        <v>1.24966283736675</v>
       </c>
       <c r="N4" t="n">
-        <v>6.77327127174281</v>
+        <v>1.784450449312188</v>
       </c>
       <c r="O4" t="n">
         <v>104.65</v>
@@ -1081,7 +1081,7 @@
         <v>0.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02582014968673</v>
+        <v>4.997891038021372</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1090,22 +1090,22 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.698501446030322</v>
+        <v>87.95629624933953</v>
       </c>
       <c r="W4" t="n">
         <v>100000</v>
       </c>
       <c r="X4" t="n">
-        <v>4.627566302823936</v>
+        <v>2.348663327355036</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3429721590593176</v>
+        <v>0.4222866559344181</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001382862412487307</v>
+        <v>0.03974249251445352</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4250068911019708</v>
+        <v>0.001745736782284338</v>
       </c>
       <c r="AB4" t="n">
         <v>0.7</v>
@@ -1114,13 +1114,13 @@
         <v>0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6266230514903539</v>
+        <v>0.002345455738722631</v>
       </c>
       <c r="AE4" t="n">
-        <v>47.02349990077214</v>
+        <v>47.29361854425881</v>
       </c>
       <c r="AF4" t="n">
-        <v>53.96066406692648</v>
+        <v>15.04798072481444</v>
       </c>
       <c r="AG4" t="n">
         <v>0.001</v>
@@ -1132,22 +1132,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.911767094867976</v>
+        <v>1.95980314550334</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.361346858936479</v>
+        <v>5.555394637208996</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.277635180932988</v>
+        <v>2.926752071628995</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.6231681070298</v>
+        <v>18.14753864329628</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AP4" t="n">
         <v>0.11</v>
@@ -1156,22 +1156,22 @@
         <v>1.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>32.76807362473758</v>
+        <v>1.38785899595586</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.610588031784961</v>
+        <v>47.30682491754626</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14193561101776</v>
+        <v>1.507634281406549</v>
       </c>
       <c r="AU4" t="n">
-        <v>188.8468654302311</v>
+        <v>29.17872262816992</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.983220746574202</v>
+        <v>18.1936222873824</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.069563355476504</v>
+        <v>1.857538550377192</v>
       </c>
       <c r="AX4" t="n">
         <v>125</v>
@@ -1233,43 +1233,43 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>64.36770230837023</v>
+        <v>81.70344380782399</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3748528187238178</v>
+        <v>0.02914083410769584</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2270316061552377</v>
+        <v>0.1027769907738974</v>
       </c>
       <c r="E5" t="n">
-        <v>15.84624982582263</v>
+        <v>2.835734535550373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05691219981859062</v>
+        <v>0.01460426442196289</v>
       </c>
       <c r="G5" t="n">
-        <v>19.04585031946194</v>
+        <v>28.98516456635008</v>
       </c>
       <c r="H5" t="n">
-        <v>6.089031615233147</v>
+        <v>2.820876156987032</v>
       </c>
       <c r="I5" t="n">
-        <v>1.812201647762723</v>
+        <v>4.793334898707079</v>
       </c>
       <c r="J5" t="n">
-        <v>5.503828499595659</v>
+        <v>3.768913731242999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.398234271374544</v>
+        <v>1.485220272111878</v>
       </c>
       <c r="L5" t="n">
-        <v>3.89410993277878</v>
+        <v>1.144756878397239</v>
       </c>
       <c r="M5" t="n">
-        <v>1.493055019962915</v>
+        <v>3.066522490478216</v>
       </c>
       <c r="N5" t="n">
-        <v>3.539405042154834</v>
+        <v>1.594028811724696</v>
       </c>
       <c r="O5" t="n">
         <v>104.65</v>
@@ -1284,7 +1284,7 @@
         <v>0.35</v>
       </c>
       <c r="S5" t="n">
-        <v>4.785443419259567</v>
+        <v>1.806574315452508</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>20.05645230145797</v>
+        <v>1.869748199744532</v>
       </c>
       <c r="W5" t="n">
         <v>100000</v>
       </c>
       <c r="X5" t="n">
-        <v>15.73581578116722</v>
+        <v>29.65393054243909</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3660281785809992</v>
+        <v>0.009888170906755261</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002346141963690441</v>
+        <v>0.1715849544091614</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1900737269589113</v>
+        <v>0.07901698818809073</v>
       </c>
       <c r="AB5" t="n">
         <v>0.7</v>
@@ -1317,13 +1317,13 @@
         <v>0.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.002112731299407956</v>
+        <v>0.0589051498733489</v>
       </c>
       <c r="AE5" t="n">
-        <v>48.88158410268331</v>
+        <v>47.14705239285698</v>
       </c>
       <c r="AF5" t="n">
-        <v>38.80350906676157</v>
+        <v>25.05588263029578</v>
       </c>
       <c r="AG5" t="n">
         <v>0.001</v>
@@ -1335,22 +1335,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.587156448539282</v>
+        <v>4.123597626033926</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.138117999412824</v>
+        <v>2.94804974202122</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.855303174240322</v>
+        <v>1.367469136529979</v>
       </c>
       <c r="AN5" t="n">
-        <v>13.46108001881788</v>
+        <v>16.40295919398157</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AP5" t="n">
         <v>0.11</v>
@@ -1359,22 +1359,22 @@
         <v>1.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.719442531004623</v>
+        <v>1.153811562099243</v>
       </c>
       <c r="AS5" t="n">
-        <v>62.20622264417224</v>
+        <v>2.137939529830414</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.434812644923747</v>
+        <v>3.007262756369808</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.25026068294205</v>
+        <v>23.16712766072778</v>
       </c>
       <c r="AV5" t="n">
-        <v>88.64368198796342</v>
+        <v>20.19739516855509</v>
       </c>
       <c r="AW5" t="n">
-        <v>15.21466995078576</v>
+        <v>14.51458998054649</v>
       </c>
       <c r="AX5" t="n">
         <v>125</v>
@@ -1436,43 +1436,43 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>3.602606114424923</v>
+        <v>71.59997520816098</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1388538247651824</v>
+        <v>0.4713234354855512</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0410270377258409</v>
+        <v>0.001123072977021321</v>
       </c>
       <c r="E6" t="n">
-        <v>6.892698035043911</v>
+        <v>29.06296971243342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004141157782578014</v>
+        <v>0.1693336587445884</v>
       </c>
       <c r="G6" t="n">
-        <v>12.24918667142058</v>
+        <v>9.610708064832668</v>
       </c>
       <c r="H6" t="n">
-        <v>9.371108732043419</v>
+        <v>5.505549700575867</v>
       </c>
       <c r="I6" t="n">
-        <v>1.559566619628675</v>
+        <v>2.610280895821241</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96729631453147</v>
+        <v>2.968116016248898</v>
       </c>
       <c r="K6" t="n">
-        <v>2.054758756990978</v>
+        <v>2.444166673814034</v>
       </c>
       <c r="L6" t="n">
-        <v>6.727960469150681</v>
+        <v>4.504986688703847</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5831836158299</v>
+        <v>1.183763443568245</v>
       </c>
       <c r="N6" t="n">
-        <v>3.991172240439826</v>
+        <v>1.054083269617909</v>
       </c>
       <c r="O6" t="n">
         <v>104.65</v>
@@ -1487,7 +1487,7 @@
         <v>0.35</v>
       </c>
       <c r="S6" t="n">
-        <v>8.104421204243254</v>
+        <v>3.989182893810989</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1496,22 +1496,22 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>47.00247555141465</v>
+        <v>3.165357962291968</v>
       </c>
       <c r="W6" t="n">
         <v>100000</v>
       </c>
       <c r="X6" t="n">
-        <v>56.06200489821757</v>
+        <v>28.39387914082847</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3767731041474493</v>
+        <v>0.01730404353339971</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3233116809809343</v>
+        <v>0.003071413917709199</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007043628874850607</v>
+        <v>0.02035408847561737</v>
       </c>
       <c r="AB6" t="n">
         <v>0.7</v>
@@ -1520,13 +1520,13 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01073450775377097</v>
+        <v>0.001639794721172315</v>
       </c>
       <c r="AE6" t="n">
-        <v>47.27592815433468</v>
+        <v>47.50275398145985</v>
       </c>
       <c r="AF6" t="n">
-        <v>71.79777819579341</v>
+        <v>43.47096254919236</v>
       </c>
       <c r="AG6" t="n">
         <v>0.001</v>
@@ -1538,22 +1538,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.085309319511053</v>
+        <v>3.444895206166115</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.643375613157378</v>
+        <v>7.436825485097111</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.133261793628876</v>
+        <v>1.494465645319397</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.95457445505195</v>
+        <v>33.91589984623916</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP6" t="n">
         <v>0.11</v>
@@ -1562,22 +1562,22 @@
         <v>1.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.35834367039238</v>
+        <v>4.021552612647521</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.396213266567</v>
+        <v>32.70365599215324</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.622416233971012</v>
+        <v>11.44806176435208</v>
       </c>
       <c r="AU6" t="n">
-        <v>15.97494070425335</v>
+        <v>8.982854933973281</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.55108633372702</v>
+        <v>6.107183347366915</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.533931222549987</v>
+        <v>2.667885716107302</v>
       </c>
       <c r="AX6" t="n">
         <v>125</v>
@@ -1639,43 +1639,43 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>20.46001491321207</v>
+        <v>9.186445702863717</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07229792908579058</v>
+        <v>0.01032206354898273</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2383471531984237</v>
+        <v>0.2375197118155644</v>
       </c>
       <c r="E7" t="n">
-        <v>4.071929236115979</v>
+        <v>2.52278417315205</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2910844104983958</v>
+        <v>0.002161220282973304</v>
       </c>
       <c r="G7" t="n">
-        <v>19.94945770203391</v>
+        <v>2.248998562279267</v>
       </c>
       <c r="H7" t="n">
-        <v>6.644794225621148</v>
+        <v>9.102540228882535</v>
       </c>
       <c r="I7" t="n">
-        <v>1.617070764142763</v>
+        <v>1.853054636676905</v>
       </c>
       <c r="J7" t="n">
-        <v>7.273379923938206</v>
+        <v>9.10302970523896</v>
       </c>
       <c r="K7" t="n">
-        <v>3.379809507238204</v>
+        <v>2.105929227621635</v>
       </c>
       <c r="L7" t="n">
-        <v>3.808458153019961</v>
+        <v>5.819589918853242</v>
       </c>
       <c r="M7" t="n">
-        <v>4.588520501255226</v>
+        <v>1.742167138335173</v>
       </c>
       <c r="N7" t="n">
-        <v>6.293513277309779</v>
+        <v>3.113126221140558</v>
       </c>
       <c r="O7" t="n">
         <v>104.65</v>
@@ -1690,7 +1690,7 @@
         <v>0.35</v>
       </c>
       <c r="S7" t="n">
-        <v>5.336223220323597</v>
+        <v>2.510858693993427</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1699,22 +1699,22 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>16.96167293845173</v>
+        <v>33.19911264233838</v>
       </c>
       <c r="W7" t="n">
         <v>100000</v>
       </c>
       <c r="X7" t="n">
-        <v>1.753672054125281</v>
+        <v>96.58048601021434</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1723671609761692</v>
+        <v>0.2497150465602352</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01213513165437068</v>
+        <v>0.0158615657712303</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001231830130551786</v>
+        <v>1.720266146012741</v>
       </c>
       <c r="AB7" t="n">
         <v>0.7</v>
@@ -1723,16 +1723,16 @@
         <v>0.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2119153312978459</v>
+        <v>0.003460449375175034</v>
       </c>
       <c r="AE7" t="n">
-        <v>47.14235109063527</v>
+        <v>48.61410445458024</v>
       </c>
       <c r="AF7" t="n">
-        <v>23.26091996216531</v>
+        <v>92.17707203103545</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="AH7" t="n">
         <v>0.11</v>
@@ -1741,19 +1741,19 @@
         <v>0.83</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.375568519354459</v>
+        <v>1.398734409166407</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.274093016152456</v>
+        <v>2.948874309869082</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.709659816801106</v>
+        <v>3.683134612424339</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.13962833846763</v>
+        <v>28.75492846884335</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
@@ -1765,22 +1765,22 @@
         <v>1.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.95134460935052</v>
+        <v>1.346778181016357</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.213109012415686</v>
+        <v>52.42200216785555</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.878226693363787</v>
+        <v>0.6078972276628447</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.427746444009603</v>
+        <v>4.646894312856268</v>
       </c>
       <c r="AV7" t="n">
-        <v>27.21304089343337</v>
+        <v>81.014832571832</v>
       </c>
       <c r="AW7" t="n">
-        <v>23.10048363179338</v>
+        <v>6.61369853923949</v>
       </c>
       <c r="AX7" t="n">
         <v>125</v>
@@ -1842,43 +1842,43 @@
         <v>24</v>
       </c>
       <c r="B8" t="n">
-        <v>3.631348331827154</v>
+        <v>12.55457780708516</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2057833138390353</v>
+        <v>0.02440400417329082</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1927203133892406</v>
+        <v>0.01193365678652883</v>
       </c>
       <c r="E8" t="n">
-        <v>17.96565667090028</v>
+        <v>4.506903875271743</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00180060276753868</v>
+        <v>0.001081817882316223</v>
       </c>
       <c r="G8" t="n">
-        <v>1.373732958318085</v>
+        <v>4.910917394889776</v>
       </c>
       <c r="H8" t="n">
-        <v>8.427846749570458</v>
+        <v>5.295639365320477</v>
       </c>
       <c r="I8" t="n">
-        <v>2.360389302058179</v>
+        <v>2.831065775285251</v>
       </c>
       <c r="J8" t="n">
-        <v>1.586752905620643</v>
+        <v>9.762022725866105</v>
       </c>
       <c r="K8" t="n">
-        <v>5.734133728895317</v>
+        <v>6.82391532362838</v>
       </c>
       <c r="L8" t="n">
-        <v>8.801406002402265</v>
+        <v>3.684173951304885</v>
       </c>
       <c r="M8" t="n">
-        <v>1.019533768185717</v>
+        <v>2.176941016983656</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2141425612504</v>
+        <v>5.541974902915644</v>
       </c>
       <c r="O8" t="n">
         <v>104.65</v>
@@ -1893,7 +1893,7 @@
         <v>0.35</v>
       </c>
       <c r="S8" t="n">
-        <v>7.574393543938275</v>
+        <v>4.721124517422286</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1902,22 +1902,22 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.218365895281829</v>
+        <v>97.02869812145943</v>
       </c>
       <c r="W8" t="n">
         <v>100000</v>
       </c>
       <c r="X8" t="n">
-        <v>24.00039018576664</v>
+        <v>89.82428950212662</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1576134195370102</v>
+        <v>0.001140559468180493</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03731880089750474</v>
+        <v>0.0202603325920751</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001286438805398578</v>
+        <v>4.455391320007288</v>
       </c>
       <c r="AB8" t="n">
         <v>0.7</v>
@@ -1926,13 +1926,13 @@
         <v>0.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.008086495768759659</v>
+        <v>0.02170406471053715</v>
       </c>
       <c r="AE8" t="n">
-        <v>48.07310137464249</v>
+        <v>47.92634481160338</v>
       </c>
       <c r="AF8" t="n">
-        <v>31.35124329103</v>
+        <v>78.42976802373988</v>
       </c>
       <c r="AG8" t="n">
         <v>0.001</v>
@@ -1944,19 +1944,19 @@
         <v>0.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.288467119283799</v>
+        <v>1.229876766661705</v>
       </c>
       <c r="AK8" t="n">
-        <v>8.927876214232013</v>
+        <v>9.778917803726236</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.746914399665526</v>
+        <v>1.056081010001009</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.36377777981046</v>
+        <v>38.99793322949121</v>
       </c>
       <c r="AO8" t="n">
         <v>1.5</v>
@@ -1968,22 +1968,22 @@
         <v>1.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.413230768898655</v>
+        <v>45.37272227579796</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.59670403309491</v>
+        <v>1.892548459437771</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.8195794752477339</v>
+        <v>3.226224420022519</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.560263490661103</v>
+        <v>82.92124224464152</v>
       </c>
       <c r="AV8" t="n">
-        <v>66.21411295442446</v>
+        <v>64.03776639300786</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.686668622286152</v>
+        <v>43.05728709072634</v>
       </c>
       <c r="AX8" t="n">
         <v>125</v>
@@ -2045,43 +2045,43 @@
         <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53014520047728</v>
+        <v>3.281320096265449</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5397355530340372</v>
+        <v>0.02386117648056063</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0959203016629217</v>
+        <v>0.4756871003239136</v>
       </c>
       <c r="E9" t="n">
-        <v>3.347896824951138</v>
+        <v>42.09314417133456</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01694378471593598</v>
+        <v>0.01429446333064133</v>
       </c>
       <c r="G9" t="n">
-        <v>12.97533673151917</v>
+        <v>43.86540292809647</v>
       </c>
       <c r="H9" t="n">
-        <v>1.542779184501955</v>
+        <v>3.636749461657438</v>
       </c>
       <c r="I9" t="n">
-        <v>1.34258758902171</v>
+        <v>4.711320208388512</v>
       </c>
       <c r="J9" t="n">
-        <v>7.595305836522888</v>
+        <v>3.546793296257681</v>
       </c>
       <c r="K9" t="n">
-        <v>3.678713439829013</v>
+        <v>9.404436005960278</v>
       </c>
       <c r="L9" t="n">
-        <v>1.10519313602445</v>
+        <v>2.091382132446103</v>
       </c>
       <c r="M9" t="n">
-        <v>4.221317313756241</v>
+        <v>4.709026922721673</v>
       </c>
       <c r="N9" t="n">
-        <v>2.080708328402839</v>
+        <v>7.08218903556156</v>
       </c>
       <c r="O9" t="n">
         <v>104.65</v>
@@ -2096,7 +2096,7 @@
         <v>0.35</v>
       </c>
       <c r="S9" t="n">
-        <v>5.859034487327534</v>
+        <v>1.905075102455216</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2105,22 +2105,22 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>83.4834170361835</v>
+        <v>2.372978136105307</v>
       </c>
       <c r="W9" t="n">
         <v>100000</v>
       </c>
       <c r="X9" t="n">
-        <v>1.263450049676087</v>
+        <v>23.19407992596669</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6521852156826869</v>
+        <v>0.2258793204008973</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001882373385000213</v>
+        <v>0.0014582770280177</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.06079936539516607</v>
+        <v>0.01072207797397361</v>
       </c>
       <c r="AB9" t="n">
         <v>0.7</v>
@@ -2129,13 +2129,13 @@
         <v>0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.09586690721381876</v>
+        <v>0.230932620613085</v>
       </c>
       <c r="AE9" t="n">
-        <v>48.28186274521521</v>
+        <v>47.59653666605058</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.39157616234573</v>
+        <v>15.50059527448968</v>
       </c>
       <c r="AG9" t="n">
         <v>0.001</v>
@@ -2147,22 +2147,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.377388487444565</v>
+        <v>3.63751890672659</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.546666752868396</v>
+        <v>7.005537602244284</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.229084202512451</v>
+        <v>5.284760147272462</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.20590379500758</v>
+        <v>33.61371478103343</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
         <v>0.11</v>
@@ -2171,22 +2171,22 @@
         <v>1.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.202403701142645</v>
+        <v>1.7094459041939</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.846065609434369</v>
+        <v>44.09172266547928</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.3986332951192066</v>
+        <v>0.4870679516534446</v>
       </c>
       <c r="AU9" t="n">
-        <v>18.87369596521525</v>
+        <v>21.27794827688885</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.162118974066749</v>
+        <v>30.89346060897748</v>
       </c>
       <c r="AW9" t="n">
-        <v>118.4069603320564</v>
+        <v>2.890901836621649</v>
       </c>
       <c r="AX9" t="n">
         <v>125</v>
@@ -2248,43 +2248,43 @@
         <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>4.124298747963138</v>
+        <v>17.91773596912573</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02755652465779577</v>
+        <v>0.1826303767697921</v>
       </c>
       <c r="D10" t="n">
-        <v>0.260395377286629</v>
+        <v>0.05486131502691064</v>
       </c>
       <c r="E10" t="n">
-        <v>1.449963428067444</v>
+        <v>2.037023944257305</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0409025918386202</v>
+        <v>0.02675161948285869</v>
       </c>
       <c r="G10" t="n">
-        <v>20.00037682192653</v>
+        <v>3.181959892514387</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1618190701351</v>
+        <v>6.805342573804791</v>
       </c>
       <c r="I10" t="n">
-        <v>3.834445568567858</v>
+        <v>3.135079376896272</v>
       </c>
       <c r="J10" t="n">
-        <v>4.272723502907298</v>
+        <v>2.379107583299622</v>
       </c>
       <c r="K10" t="n">
-        <v>2.538824129988674</v>
+        <v>4.22184533988398</v>
       </c>
       <c r="L10" t="n">
-        <v>9.158910818074796</v>
+        <v>1.173537986594373</v>
       </c>
       <c r="M10" t="n">
-        <v>2.274793521092383</v>
+        <v>1.719762024872556</v>
       </c>
       <c r="N10" t="n">
-        <v>2.092730381121173</v>
+        <v>2.310478898298407</v>
       </c>
       <c r="O10" t="n">
         <v>104.65</v>
@@ -2299,7 +2299,7 @@
         <v>0.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.154988580449666</v>
+        <v>1.742274011694833</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2308,22 +2308,22 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.40323748697024</v>
+        <v>24.56696209538416</v>
       </c>
       <c r="W10" t="n">
         <v>100000</v>
       </c>
       <c r="X10" t="n">
-        <v>50.22122810108576</v>
+        <v>4.055155578091554</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7090047477438292</v>
+        <v>0.1317603781012531</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.004992063101226683</v>
+        <v>0.01664471254655459</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7435631518680565</v>
+        <v>0.2689754796203033</v>
       </c>
       <c r="AB10" t="n">
         <v>0.7</v>
@@ -2332,13 +2332,13 @@
         <v>0.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0038491645235865</v>
+        <v>0.003417769519140669</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.55143382181333</v>
+        <v>47.81428710873787</v>
       </c>
       <c r="AF10" t="n">
-        <v>59.86690840058926</v>
+        <v>17.92669840983086</v>
       </c>
       <c r="AG10" t="n">
         <v>0.001</v>
@@ -2350,22 +2350,22 @@
         <v>0.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.513219119253475</v>
+        <v>3.331302081669874</v>
       </c>
       <c r="AK10" t="n">
-        <v>8.278789881553323</v>
+        <v>1.511690506826077</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.337142006274751</v>
+        <v>1.285971123125979</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.6880291168801</v>
+        <v>30.82536353418623</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP10" t="n">
         <v>0.11</v>
@@ -2374,22 +2374,22 @@
         <v>1.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.417105488015442</v>
+        <v>1.092091572934176</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.268427739293822</v>
+        <v>10.73637355985257</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.580220922955504</v>
+        <v>0.9754019880475571</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.995669022584384</v>
+        <v>8.329316792834856</v>
       </c>
       <c r="AV10" t="n">
-        <v>35.03387564812819</v>
+        <v>23.8528027502881</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.05868985289973</v>
+        <v>2.861640185317263</v>
       </c>
       <c r="AX10" t="n">
         <v>125</v>
